--- a/diseases/d239/2015-2019.xlsx
+++ b/diseases/d239/2015-2019.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20566,7 +20566,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21347,7 +21347,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23690,7 +23690,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26033,7 +26033,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26814,7 +26814,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28376,7 +28376,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29157,7 +29157,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30719,7 +30719,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31500,7 +31500,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32281,7 +32281,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33843,7 +33843,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34624,7 +34624,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35405,7 +35405,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36186,7 +36186,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36967,7 +36967,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37748,7 +37748,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38529,7 +38529,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39310,7 +39310,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40091,7 +40091,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -40872,7 +40872,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41653,7 +41653,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42434,7 +42434,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">

--- a/diseases/d239/2015-2019.xlsx
+++ b/diseases/d239/2015-2019.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20566,7 +20566,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21347,7 +21347,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23690,7 +23690,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26033,7 +26033,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26814,7 +26814,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28376,7 +28376,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29157,7 +29157,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30719,7 +30719,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31500,7 +31500,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32281,7 +32281,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33843,7 +33843,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34624,7 +34624,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35405,7 +35405,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36186,7 +36186,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36967,7 +36967,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37748,7 +37748,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38529,7 +38529,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39310,7 +39310,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40091,7 +40091,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -40872,7 +40872,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41653,7 +41653,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42434,7 +42434,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
